--- a/data/Sucursales_asistencia_final.xlsx
+++ b/data/Sucursales_asistencia_final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vladimir\Documents\Reportes\Analisis_deportivo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2E6BD64-48C2-42D3-96AB-6A0E14AD3757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240401B8-69C7-46BF-9DA2-C8725BEAE933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AC6E86AB-2722-4AB1-A4AE-B45BB56BA53E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$B$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>SANTA FE</t>
   </si>
@@ -112,6 +112,15 @@
   </si>
   <si>
     <t>Asistencia al 30 nov</t>
+  </si>
+  <si>
+    <t>METEPEC</t>
+  </si>
+  <si>
+    <t>TLALNEPANTLA</t>
+  </si>
+  <si>
+    <t>SALTILLO VILLALTA</t>
   </si>
 </sst>
 </file>
@@ -153,10 +162,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -181,7 +193,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4423FCD-DCE1-4F07-A524-6D767349A9C6}" name="Tabla1" displayName="Tabla1" ref="A1:C23" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4423FCD-DCE1-4F07-A524-6D767349A9C6}" name="Tabla1" displayName="Tabla1" ref="A1:C26" totalsRowShown="0">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B23">
     <sortCondition ref="A1:A23"/>
   </sortState>
@@ -491,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA263BAA-41E0-445C-B0EF-58913FE6750F}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
@@ -751,6 +763,30 @@
         <v>1462</v>
       </c>
     </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
